--- a/astro-site/public/dl/plan-chef-privado-showcooking-eventos/checklist-apertura-chef-privado-showcooking.xlsx
+++ b/astro-site/public/dl/plan-chef-privado-showcooking-eventos/checklist-apertura-chef-privado-showcooking.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist 6 fases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Checklist 6 fases'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -479,7 +481,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -506,6 +508,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1013,6 +1016,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr"/>
     </row>
+    <row r="24"/>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
@@ -1254,6 +1258,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr"/>
     </row>
+    <row r="35"/>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
@@ -1963,6 +1968,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr"/>
     </row>
+    <row r="64"/>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
@@ -2412,6 +2418,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr"/>
     </row>
+    <row r="83"/>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
@@ -2809,6 +2816,7 @@
       </c>
       <c r="F99" s="5" t="inlineStr"/>
     </row>
+    <row r="100"/>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
@@ -3286,15 +3294,24 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A65:F65"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="A84:F84"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A101:F101"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>